--- a/artfynd/A 42577-2023 artfynd.xlsx
+++ b/artfynd/A 42577-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 42577-2023 artfynd.xlsx
+++ b/artfynd/A 42577-2023 artfynd.xlsx
@@ -1553,7 +1553,7 @@
         <v>117835862</v>
       </c>
       <c r="B9" t="n">
-        <v>57534</v>
+        <v>57535</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 42577-2023 artfynd.xlsx
+++ b/artfynd/A 42577-2023 artfynd.xlsx
@@ -1674,10 +1674,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118414114</v>
+        <v>118414078</v>
       </c>
       <c r="B10" t="n">
-        <v>56502</v>
+        <v>57443</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1686,41 +1686,37 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1802,10 +1798,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118414078</v>
+        <v>118414114</v>
       </c>
       <c r="B11" t="n">
-        <v>57443</v>
+        <v>56502</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1814,37 +1810,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>

--- a/artfynd/A 42577-2023 artfynd.xlsx
+++ b/artfynd/A 42577-2023 artfynd.xlsx
@@ -1674,10 +1674,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118414078</v>
+        <v>118414114</v>
       </c>
       <c r="B10" t="n">
-        <v>57443</v>
+        <v>56502</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1686,37 +1686,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1798,10 +1802,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118414114</v>
+        <v>118414078</v>
       </c>
       <c r="B11" t="n">
-        <v>56502</v>
+        <v>57443</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1810,41 +1814,37 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>

--- a/artfynd/A 42577-2023 artfynd.xlsx
+++ b/artfynd/A 42577-2023 artfynd.xlsx
@@ -1677,7 +1677,7 @@
         <v>118414114</v>
       </c>
       <c r="B10" t="n">
-        <v>56584</v>
+        <v>56589</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 42577-2023 artfynd.xlsx
+++ b/artfynd/A 42577-2023 artfynd.xlsx
@@ -1692,11 +1692,6 @@
       <c r="E10" t="n">
         <v>100138</v>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Tjäder</t>
-        </is>
-      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>Tetrao urogallus</t>

--- a/artfynd/A 42577-2023 artfynd.xlsx
+++ b/artfynd/A 42577-2023 artfynd.xlsx
@@ -1677,7 +1677,7 @@
         <v>118414114</v>
       </c>
       <c r="B10" t="n">
-        <v>56589</v>
+        <v>56593</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1691,6 +1691,11 @@
       </c>
       <c r="E10" t="n">
         <v>100138</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>

--- a/artfynd/A 42577-2023 artfynd.xlsx
+++ b/artfynd/A 42577-2023 artfynd.xlsx
@@ -1677,7 +1677,7 @@
         <v>118414114</v>
       </c>
       <c r="B10" t="n">
-        <v>56593</v>
+        <v>56594</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 42577-2023 artfynd.xlsx
+++ b/artfynd/A 42577-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1800,130 +1800,6 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>118414078</v>
-      </c>
-      <c r="B11" t="n">
-        <v>57445</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Stenby O, Tosterön, Srm</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>615172</v>
-      </c>
-      <c r="R11" t="n">
-        <v>6587004</v>
-      </c>
-      <c r="S11" t="n">
-        <v>50</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Strängnäs</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Aspö</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2024-07-13</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2024-07-13</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AD11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>Markku Kemppi</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>Markku Kemppi</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
